--- a/data/trans_orig/P6712-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2012</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35577</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44460</t>
+          <t>44351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62789</t>
+          <t>60981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86341</t>
+          <t>85448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>61792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112617</t>
+          <t>112009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141720</t>
+          <t>143079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>30160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39945</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>33054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>33817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>33727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60504</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101350</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127995</t>
+          <t>128360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63303</t>
+          <t>63312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86222</t>
+          <t>86204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174423</t>
+          <t>173796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209166</t>
+          <t>207549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -2095,82 +2095,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7832</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7931</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2991</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35471</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51684</t>
+          <t>51321</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53279</t>
+          <t>53615</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>44318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>69190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60884</t>
+          <t>60851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84105</t>
+          <t>84103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38802</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107052</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135941</t>
+          <t>134510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29822</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>53042</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>42893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50804</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80439</t>
+          <t>78196</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69221</t>
+          <t>69678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93773</t>
+          <t>93991</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>34826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110517</t>
+          <t>110551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>145201</t>
+          <t>142215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>32802</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>45104</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24122</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>7298</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>2114</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>6708</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>7023</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14836</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>34368</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>45897</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>46849</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>54034</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>77590</t>
+          <t>77846</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>79948</t>
+          <t>82810</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>108120</t>
+          <t>107850</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>55790</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>40598</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>55577</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>88386</t>
+          <t>86215</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>41423</t>
+          <t>41871</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>29960</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>55034</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>113150</t>
+          <t>113237</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>137545</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>170491</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>83858</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>111847</t>
+          <t>111744</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>229766</t>
+          <t>228598</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>272246</t>
+          <t>275298</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>36277</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>44137</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>74646</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>40412</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>68097</t>
+          <t>67935</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>93998</t>
+          <t>92154</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>134960</t>
+          <t>131638</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>121721</t>
+          <t>121712</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>160470</t>
+          <t>160139</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>84814</t>
+          <t>85642</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>117811</t>
+          <t>118867</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>218620</t>
+          <t>216940</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>266426</t>
+          <t>268371</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>114744</t>
+          <t>114833</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>153764</t>
+          <t>151560</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>72300</t>
+          <t>71884</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>104740</t>
+          <t>102901</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>198232</t>
+          <t>198085</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>246775</t>
+          <t>244709</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>76263</t>
+          <t>75840</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>56963</t>
+          <t>58312</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>84245</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>123871</t>
+          <t>125607</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>82990</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>84691</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>126713</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>198243</t>
+          <t>197806</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>255103</t>
+          <t>253934</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>139925</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>187434</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>351183</t>
+          <t>348875</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>429729</t>
+          <t>420571</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>297758</t>
+          <t>303730</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>365939</t>
+          <t>370714</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>216212</t>
+          <t>214922</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>277087</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>536587</t>
+          <t>535360</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>625118</t>
+          <t>622905</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>695358</t>
+          <t>690323</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>772978</t>
+          <t>768325</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>416587</t>
+          <t>420656</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>482083</t>
+          <t>484486</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1131316</t>
+          <t>1131288</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1232799</t>
+          <t>1235484</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2016</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37913</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42238</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51159</t>
+          <t>51358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28732</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22277</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43066</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>47046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71103</t>
+          <t>70933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63339</t>
+          <t>63890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95521</t>
+          <t>96091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126925</t>
+          <t>128275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37505</t>
+          <t>38618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47948</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>42987</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70413</t>
+          <t>70478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>54447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74791</t>
+          <t>75132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>51074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77661</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35466</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>58016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96157</t>
+          <t>93688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128374</t>
+          <t>127392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37973</t>
+          <t>37535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>29930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62191</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58125</t>
+          <t>57238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46749</t>
+          <t>46269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72080</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99022</t>
+          <t>98951</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>74815</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20152</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20431</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68837</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88947</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42578</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>58699</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115938</t>
+          <t>115025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>141290</t>
+          <t>142303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>19594</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53371</t>
+          <t>53342</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46740</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>66856</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22879</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>38949</t>
+          <t>39555</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>39561</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>64687</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t>43092</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>31923</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>69971</t>
+          <t>68420</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>30718</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>54276</t>
+          <t>54282</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>29459</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>56791</t>
+          <t>56550</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>28991</t>
+          <t>29253</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>66739</t>
+          <t>65717</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>99736</t>
+          <t>99271</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>82849</t>
+          <t>86318</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>121094</t>
+          <t>122497</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59709</t>
+          <t>59874</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>88301</t>
+          <t>87274</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>153247</t>
+          <t>156686</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>201744</t>
+          <t>200694</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>84218</t>
+          <t>84074</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>55886</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>85671</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>114094</t>
+          <t>117732</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>160285</t>
+          <t>159278</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>99995</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>141820</t>
+          <t>138997</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>73132</t>
+          <t>72015</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>104846</t>
+          <t>102839</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>184266</t>
+          <t>183127</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>236221</t>
+          <t>233447</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>34158</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>42148</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>69462</t>
+          <t>68034</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>39891</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>65631</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>88243</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>125844</t>
+          <t>125732</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>116252</t>
+          <t>116049</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>150326</t>
+          <t>151739</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>70848</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>100354</t>
+          <t>102078</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>195776</t>
+          <t>196724</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>243351</t>
+          <t>243869</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>109701</t>
+          <t>107578</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>143792</t>
+          <t>144524</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>74194</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>105652</t>
+          <t>104417</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>193271</t>
+          <t>191129</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>240187</t>
+          <t>238828</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>85565</t>
+          <t>86108</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>74665</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>104357</t>
+          <t>105542</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>150354</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>84348</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>122642</t>
+          <t>120147</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,47 +12724,47 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>225454</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>200005</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>256263</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>225454</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>198031</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>256569</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>279019</t>
+          <t>277644</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>340812</t>
+          <t>342219</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>202914</t>
+          <t>204091</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>257401</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>496863</t>
+          <t>501122</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>579647</t>
+          <t>587496</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>359026</t>
+          <t>359690</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>426156</t>
+          <t>425206</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>250976</t>
+          <t>251409</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>306827</t>
+          <t>310178</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>626956</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>719610</t>
+          <t>720969</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>493187</t>
+          <t>494012</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>566456</t>
+          <t>566863</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>339872</t>
+          <t>338875</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>395734</t>
+          <t>398800</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>849429</t>
+          <t>847458</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>946415</t>
+          <t>945711</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6712-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>43812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26224</t>
+          <t>26955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>63943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85448</t>
+          <t>87325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42172</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61792</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112009</t>
+          <t>112345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143079</t>
+          <t>142565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30160</t>
+          <t>29407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38879</t>
+          <t>38857</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33054</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>59977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102889</t>
+          <t>103873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128360</t>
+          <t>128806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>63281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86204</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173796</t>
+          <t>174129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207549</t>
+          <t>207713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>23004</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29501</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51321</t>
+          <t>52628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31771</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53615</t>
+          <t>53635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>23135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44318</t>
+          <t>43261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69190</t>
+          <t>69754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>60118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84103</t>
+          <t>84084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>37903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134510</t>
+          <t>134729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53042</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42893</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>43565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78196</t>
+          <t>79905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69678</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>35908</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>55666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110551</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142215</t>
+          <t>143965</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>32076</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45104</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>24623</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>62868</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>33323</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46849</t>
+          <t>46997</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>55325</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>77846</t>
+          <t>77273</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>35823</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>82810</t>
+          <t>80946</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>107850</t>
+          <t>108412</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>54656</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40598</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>55577</t>
+          <t>56306</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>86215</t>
+          <t>90057</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>41871</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>68309</t>
+          <t>68176</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>52371</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>77760</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>113237</t>
+          <t>112079</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>136731</t>
+          <t>136359</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>168037</t>
+          <t>170712</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>83858</t>
+          <t>83727</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>111744</t>
+          <t>111655</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>228598</t>
+          <t>227009</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>275298</t>
+          <t>273448</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,49 +5633,49 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>8542</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>17977</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
           <t>6,93%</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>8542</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>16451</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>36277</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>72858</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>40412</t>
+          <t>41148</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>67935</t>
+          <t>68255</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>92154</t>
+          <t>93042</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>131638</t>
+          <t>131604</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>121712</t>
+          <t>122917</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>160139</t>
+          <t>162420</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>118867</t>
+          <t>118562</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>216940</t>
+          <t>215688</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>268371</t>
+          <t>270483</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>114833</t>
+          <t>112257</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>151560</t>
+          <t>150822</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>71884</t>
+          <t>72322</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>102901</t>
+          <t>105161</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>198085</t>
+          <t>194220</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>244709</t>
+          <t>244095</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>45490</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>83713</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>125607</t>
+          <t>123935</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>88348</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129942</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>197806</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>253934</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>139050</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>187434</t>
+          <t>188814</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>348875</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>420571</t>
+          <t>425094</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>303730</t>
+          <t>302679</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>370714</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>214922</t>
+          <t>218695</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>274046</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>535360</t>
+          <t>538478</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>622905</t>
+          <t>626723</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>690323</t>
+          <t>692765</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>768325</t>
+          <t>769119</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>420656</t>
+          <t>419379</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>484486</t>
+          <t>482649</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1131288</t>
+          <t>1131563</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1235484</t>
+          <t>1236458</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37693</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>42372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26908</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51358</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>18683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70933</t>
+          <t>70186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63890</t>
+          <t>64740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96091</t>
+          <t>94928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128275</t>
+          <t>127494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>20914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38618</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70478</t>
+          <t>70057</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>31265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54447</t>
+          <t>55214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47373</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75132</t>
+          <t>77733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51074</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77332</t>
+          <t>77030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58016</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93688</t>
+          <t>93113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127392</t>
+          <t>127924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37535</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>14296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57238</t>
+          <t>58098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>46793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>71579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98951</t>
+          <t>97635</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>33278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>53329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>26934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49020</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74815</t>
+          <t>74382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>36306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68118</t>
+          <t>66876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>87980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58699</t>
+          <t>59929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115025</t>
+          <t>115490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142303</t>
+          <t>142266</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53342</t>
+          <t>53590</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>45863</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>26780</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43997</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66856</t>
+          <t>66915</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64687</t>
+          <t>63480</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24036</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31923</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>43338</t>
+          <t>45255</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>68420</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>39992</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>54282</t>
+          <t>53774</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39255</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23502</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>31067</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>56550</t>
+          <t>56645</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>52170</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>65717</t>
+          <t>65274</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>99271</t>
+          <t>99439</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>86318</t>
+          <t>85781</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>122497</t>
+          <t>121589</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59874</t>
+          <t>60869</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>87274</t>
+          <t>91021</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>156686</t>
+          <t>155507</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>200694</t>
+          <t>201573</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>54393</t>
+          <t>52474</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>84074</t>
+          <t>84327</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>55258</t>
+          <t>55248</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>85671</t>
+          <t>83743</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>117732</t>
+          <t>116748</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>159278</t>
+          <t>159148</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>99995</t>
+          <t>101321</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>138997</t>
+          <t>139556</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>72015</t>
+          <t>73350</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>102839</t>
+          <t>102821</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>183127</t>
+          <t>184469</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>233447</t>
+          <t>235031</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>34158</t>
+          <t>33318</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>42148</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>68034</t>
+          <t>69023</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>40085</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>64821</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>90598</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>125732</t>
+          <t>127636</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>116049</t>
+          <t>116048</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>151739</t>
+          <t>151301</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>70635</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>102078</t>
+          <t>100954</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>196724</t>
+          <t>194910</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>243869</t>
+          <t>240660</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>107988</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>144524</t>
+          <t>142933</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>72750</t>
+          <t>75286</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>104417</t>
+          <t>105036</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>191129</t>
+          <t>192652</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>238828</t>
+          <t>239426</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>54016</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>88525</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>74000</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>105542</t>
+          <t>104826</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>150354</t>
+          <t>147456</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>103918</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>144669</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>83913</t>
+          <t>83523</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>120147</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>197916</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>256263</t>
+          <t>255823</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>275076</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>341572</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>204091</t>
+          <t>204281</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>257401</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>501122</t>
+          <t>497493</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>587496</t>
+          <t>579444</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>359690</t>
+          <t>359997</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>425206</t>
+          <t>422348</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>251409</t>
+          <t>250287</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>310178</t>
+          <t>308100</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>626956</t>
+          <t>625388</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>720969</t>
+          <t>713647</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>494012</t>
+          <t>494847</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>566863</t>
+          <t>567744</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>338875</t>
+          <t>338261</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>398800</t>
+          <t>399826</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>847458</t>
+          <t>848788</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>945711</t>
+          <t>951257</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
